--- a/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
@@ -335,23 +335,65 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="2160"/>
+          <min val="2100"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>m above sea level</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -562,23 +604,65 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1995"/>
+          <min val="1970"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>m above sea level</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="5"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -973,6 +1057,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -997,10 +1082,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Not covered: Daule-Peripa (CELEC Hidronacion) and Pisayambo (CELEC Hidroagoyan) - those units publish no machine-readable level series.</t>
+          <t>Not covered: Daule-Peripa (CELEC Hidronacion) and Pisayambo (CELEC Hidroagoyan) - no public level series found: their CELEC sites have no production/level dashboard like CELEC SUR's, and CENACE's Informacion Operativa page (checked Oct-2026) has generation by plant but no reservoir levels.</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -1022,6 +1108,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
@@ -23904,7 +23991,7 @@
         <v>1986.93</v>
       </c>
       <c r="D310" t="n">
-        <v>96.59999999999999</v>
+        <v>96.5</v>
       </c>
     </row>
     <row r="311">
@@ -41054,7 +41141,7 @@
         <v>1980.3</v>
       </c>
       <c r="D1535" t="n">
-        <v>57</v>
+        <v>56.9</v>
       </c>
     </row>
     <row r="1536">
@@ -41096,7 +41183,7 @@
         <v>1981.63</v>
       </c>
       <c r="D1538" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="1539">
@@ -41964,7 +42051,7 @@
         <v>1990.83</v>
       </c>
       <c r="D1600" t="n">
-        <v>100.2</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="1601">
@@ -42482,7 +42569,7 @@
         <v>1991.24</v>
       </c>
       <c r="D1637" t="n">
-        <v>101.6</v>
+        <v>101.7</v>
       </c>
     </row>
     <row r="1638">
@@ -42762,7 +42849,7 @@
         <v>1980.58</v>
       </c>
       <c r="D1657" t="n">
-        <v>99.59999999999999</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="1658">
@@ -42832,7 +42919,7 @@
         <v>1980.55</v>
       </c>
       <c r="D1662" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="1663">
@@ -42944,7 +43031,7 @@
         <v>1981.28</v>
       </c>
       <c r="D1670" t="n">
-        <v>100.6</v>
+        <v>100.7</v>
       </c>
     </row>
     <row r="1671">
@@ -43238,7 +43325,7 @@
         <v>1990.52</v>
       </c>
       <c r="D1691" t="n">
-        <v>100</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="1692">
@@ -43658,7 +43745,7 @@
         <v>1983.25</v>
       </c>
       <c r="D1721" t="n">
-        <v>94.40000000000001</v>
+        <v>94.3</v>
       </c>
     </row>
     <row r="1722">
@@ -43686,7 +43773,7 @@
         <v>1982.7</v>
       </c>
       <c r="D1723" t="n">
-        <v>93</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="1724">
@@ -44904,7 +44991,7 @@
         <v>1983.44</v>
       </c>
       <c r="D1810" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
     </row>
     <row r="1811">
@@ -45548,7 +45635,7 @@
         <v>1978.37</v>
       </c>
       <c r="D1856" t="n">
-        <v>65.2</v>
+        <v>65.3</v>
       </c>
     </row>
     <row r="1857">
@@ -45674,7 +45761,7 @@
         <v>1982.53</v>
       </c>
       <c r="D1865" t="n">
-        <v>59.4</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="1866">
@@ -45702,7 +45789,7 @@
         <v>1985.3</v>
       </c>
       <c r="D1867" t="n">
-        <v>62</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="1868">
@@ -45954,7 +46041,7 @@
         <v>1981.79</v>
       </c>
       <c r="D1885" t="n">
-        <v>64.2</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="1886">
@@ -47284,7 +47371,7 @@
         <v>1990.34</v>
       </c>
       <c r="D1980" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="1981">
@@ -47368,7 +47455,7 @@
         <v>1990.62</v>
       </c>
       <c r="D1986" t="n">
-        <v>101.2</v>
+        <v>101.3</v>
       </c>
     </row>
     <row r="1987">
@@ -48376,7 +48463,7 @@
         <v>1990.89</v>
       </c>
       <c r="D2058" t="n">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
     </row>
     <row r="2059">
@@ -48754,7 +48841,7 @@
         <v>1985.03</v>
       </c>
       <c r="D2085" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="2086">
@@ -49496,7 +49583,7 @@
         <v>1983.22</v>
       </c>
       <c r="D2138" t="n">
-        <v>78</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="2139">
@@ -49636,7 +49723,7 @@
         <v>1981.18</v>
       </c>
       <c r="D2148" t="n">
-        <v>77.59999999999999</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="2149">
@@ -49650,7 +49737,7 @@
         <v>1981.1</v>
       </c>
       <c r="D2149" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="2150">
@@ -50210,7 +50297,7 @@
         <v>1981.1</v>
       </c>
       <c r="D2189" t="n">
-        <v>74.40000000000001</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="2190">
@@ -50336,7 +50423,7 @@
         <v>1981.52</v>
       </c>
       <c r="D2198" t="n">
-        <v>76.8</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="2199">
@@ -50434,7 +50521,7 @@
         <v>1981.79</v>
       </c>
       <c r="D2205" t="n">
-        <v>84.40000000000001</v>
+        <v>84.3</v>
       </c>
     </row>
     <row r="2206">
@@ -50630,7 +50717,7 @@
         <v>1982.97</v>
       </c>
       <c r="D2219" t="n">
-        <v>84</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="2220">
@@ -51302,7 +51389,7 @@
         <v>1990.96</v>
       </c>
       <c r="D2267" t="n">
-        <v>102.2</v>
+        <v>102.3</v>
       </c>
     </row>
     <row r="2268">
@@ -52730,7 +52817,7 @@
         <v>1990.87</v>
       </c>
       <c r="D2369" t="n">
-        <v>100.2</v>
+        <v>100.3</v>
       </c>
     </row>
     <row r="2370">
@@ -53150,7 +53237,7 @@
         <v>1991.35</v>
       </c>
       <c r="D2399" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="2400">
@@ -53318,7 +53405,7 @@
         <v>1988.53</v>
       </c>
       <c r="D2411" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
     </row>
     <row r="2412">
@@ -53332,7 +53419,7 @@
         <v>1988.9</v>
       </c>
       <c r="D2412" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
     </row>
     <row r="2413">
@@ -53920,7 +54007,7 @@
         <v>1987.94</v>
       </c>
       <c r="D2454" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
     </row>
     <row r="2455">
@@ -54494,7 +54581,7 @@
         <v>1987.03</v>
       </c>
       <c r="D2495" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
     </row>
     <row r="2496">
@@ -54536,7 +54623,7 @@
         <v>1987.55</v>
       </c>
       <c r="D2498" t="n">
-        <v>97.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="2499">
@@ -54550,7 +54637,7 @@
         <v>1987.31</v>
       </c>
       <c r="D2499" t="n">
-        <v>97.59999999999999</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="2500">
@@ -54578,7 +54665,7 @@
         <v>1987.91</v>
       </c>
       <c r="D2501" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="2502">
@@ -54928,7 +55015,7 @@
         <v>1985.26</v>
       </c>
       <c r="D2526" t="n">
-        <v>88.8</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="2527">
@@ -55432,7 +55519,7 @@
         <v>1986.93</v>
       </c>
       <c r="D2562" t="n">
-        <v>81.59999999999999</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="2563">
@@ -56118,7 +56205,7 @@
         <v>1987.09</v>
       </c>
       <c r="D2611" t="n">
-        <v>61.8</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="2612">
@@ -56202,7 +56289,7 @@
         <v>1985.33</v>
       </c>
       <c r="D2617" t="n">
-        <v>54.6</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="2618">
@@ -56356,7 +56443,7 @@
         <v>1984.41</v>
       </c>
       <c r="D2628" t="n">
-        <v>53.8</v>
+        <v>53.7</v>
       </c>
     </row>
     <row r="2629">
@@ -56398,7 +56485,7 @@
         <v>1985.38</v>
       </c>
       <c r="D2631" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
     </row>
     <row r="2632">
@@ -56454,7 +56541,7 @@
         <v>1981.35</v>
       </c>
       <c r="D2635" t="n">
-        <v>47</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="2636">
@@ -56594,7 +56681,7 @@
         <v>1981.82</v>
       </c>
       <c r="D2645" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="2646">
@@ -74164,7 +74251,7 @@
         <v>1982.25</v>
       </c>
       <c r="D3900" t="n">
-        <v>86.40000000000001</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="3901">
@@ -80016,7 +80103,7 @@
         <v>1985.32</v>
       </c>
       <c r="D4318" t="n">
-        <v>87.8</v>
+        <v>87.90000000000001</v>
       </c>
     </row>
     <row r="4319">
@@ -81346,7 +81433,7 @@
         <v>1978.65</v>
       </c>
       <c r="D4413" t="n">
-        <v>58</v>
+        <v>57.9</v>
       </c>
     </row>
     <row r="4414">
@@ -84356,7 +84443,7 @@
         <v>1988.08</v>
       </c>
       <c r="D4628" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="4629">
@@ -84874,7 +84961,7 @@
         <v>1976.55</v>
       </c>
       <c r="D4665" t="n">
-        <v>59</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="4666">
@@ -85560,7 +85647,7 @@
         <v>1980.37</v>
       </c>
       <c r="D4714" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="4715">
@@ -85742,7 +85829,7 @@
         <v>1982.14</v>
       </c>
       <c r="D4727" t="n">
-        <v>46</v>
+        <v>45.9</v>
       </c>
     </row>
     <row r="4728">
@@ -85896,7 +85983,7 @@
         <v>1985.3</v>
       </c>
       <c r="D4738" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
     </row>
     <row r="4739">
@@ -85938,7 +86025,7 @@
         <v>1984.78</v>
       </c>
       <c r="D4741" t="n">
-        <v>59.6</v>
+        <v>59.5</v>
       </c>
     </row>
     <row r="4742">
@@ -86106,7 +86193,7 @@
         <v>1984.67</v>
       </c>
       <c r="D4753" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="4754">
@@ -86134,7 +86221,7 @@
         <v>1984.66</v>
       </c>
       <c r="D4755" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
     </row>
     <row r="4756">
@@ -86302,7 +86389,7 @@
         <v>1985.87</v>
       </c>
       <c r="D4767" t="n">
-        <v>85.40000000000001</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="4768">
@@ -89816,7 +89903,7 @@
         <v>1985.93</v>
       </c>
       <c r="D5018" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="5019">
@@ -89984,7 +90071,7 @@
         <v>1983.32</v>
       </c>
       <c r="D5030" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="5031">
@@ -90082,7 +90169,7 @@
         <v>1981.64</v>
       </c>
       <c r="D5037" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
     </row>
     <row r="5038">
@@ -90460,7 +90547,7 @@
         <v>1982.26</v>
       </c>
       <c r="D5064" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="5065">
@@ -90502,7 +90589,7 @@
         <v>1979.92</v>
       </c>
       <c r="D5067" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="5068">
@@ -90670,7 +90757,7 @@
         <v>1982.04</v>
       </c>
       <c r="D5079" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="5080">
@@ -90894,7 +90981,7 @@
         <v>1984.39</v>
       </c>
       <c r="D5095" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="5096">
@@ -90908,7 +90995,7 @@
         <v>1983.76</v>
       </c>
       <c r="D5096" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="5097">
@@ -90922,7 +91009,7 @@
         <v>1982.44</v>
       </c>
       <c r="D5097" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
     </row>
     <row r="5098">
@@ -91132,7 +91219,7 @@
         <v>1985.9</v>
       </c>
       <c r="D5112" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="5113">
@@ -91356,7 +91443,7 @@
         <v>1987.25</v>
       </c>
       <c r="D5128" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="5129">
@@ -91748,7 +91835,7 @@
         <v>1985.65</v>
       </c>
       <c r="D5156" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="5157">

--- a/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
@@ -154,7 +154,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-07</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -423,7 +423,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-07</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1068,7 +1068,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-Jan-2011 to 01-Oct-2026 (5,753 days). Latest Mazar 2130.89 m (60% of range) on 01-Oct-2026.</t>
+          <t>01-Jan-2011 to 07-Oct-2026 (5,759 days). Latest Mazar 2130.07 m (58% of range) on 07-Oct-2026.</t>
         </is>
       </c>
     </row>
@@ -1246,6 +1246,9 @@
       <c r="F3" t="n">
         <v>2153.2</v>
       </c>
+      <c r="G3" t="n">
+        <v>2130.46</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1268,6 +1271,9 @@
       <c r="F4" t="n">
         <v>2153.55</v>
       </c>
+      <c r="G4" t="n">
+        <v>2131.12</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1290,6 +1296,9 @@
       <c r="F5" t="n">
         <v>2153.45</v>
       </c>
+      <c r="G5" t="n">
+        <v>2132.05</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1312,6 +1321,9 @@
       <c r="F6" t="n">
         <v>2153.23</v>
       </c>
+      <c r="G6" t="n">
+        <v>2131.96</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1334,6 +1346,9 @@
       <c r="F7" t="n">
         <v>2153.03</v>
       </c>
+      <c r="G7" t="n">
+        <v>2131.27</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1355,6 +1370,9 @@
       </c>
       <c r="F8" t="n">
         <v>2152.63</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2130.07</v>
       </c>
     </row>
     <row r="9">
@@ -9405,6 +9423,9 @@
       <c r="F3" t="n">
         <v>1990.41</v>
       </c>
+      <c r="G3" t="n">
+        <v>1985.67</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9427,6 +9448,9 @@
       <c r="F4" t="n">
         <v>1990.88</v>
       </c>
+      <c r="G4" t="n">
+        <v>1985.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9449,6 +9473,9 @@
       <c r="F5" t="n">
         <v>1990.76</v>
       </c>
+      <c r="G5" t="n">
+        <v>1985.13</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9471,6 +9498,9 @@
       <c r="F6" t="n">
         <v>1990.49</v>
       </c>
+      <c r="G6" t="n">
+        <v>1983.49</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9493,6 +9523,9 @@
       <c r="F7" t="n">
         <v>1990.34</v>
       </c>
+      <c r="G7" t="n">
+        <v>1981.69</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9514,6 +9547,9 @@
       </c>
       <c r="F8" t="n">
         <v>1990.43</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1981.07</v>
       </c>
     </row>
     <row r="9">
@@ -17459,7 +17495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5754"/>
+  <dimension ref="A1:D5760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98024,6 +98060,90 @@
       </c>
       <c r="D5754" t="n">
         <v>59.8</v>
+      </c>
+    </row>
+    <row r="5755">
+      <c r="A5755" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B5755" t="n">
+        <v>2130.46</v>
+      </c>
+      <c r="C5755" t="n">
+        <v>1985.67</v>
+      </c>
+      <c r="D5755" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5756">
+      <c r="A5756" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B5756" t="n">
+        <v>2131.12</v>
+      </c>
+      <c r="C5756" t="n">
+        <v>1985.5</v>
+      </c>
+      <c r="D5756" t="n">
+        <v>60.2</v>
+      </c>
+    </row>
+    <row r="5757">
+      <c r="A5757" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B5757" t="n">
+        <v>2132.05</v>
+      </c>
+      <c r="C5757" t="n">
+        <v>1985.13</v>
+      </c>
+      <c r="D5757" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="5758">
+      <c r="A5758" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B5758" t="n">
+        <v>2131.96</v>
+      </c>
+      <c r="C5758" t="n">
+        <v>1983.49</v>
+      </c>
+      <c r="D5758" t="n">
+        <v>61.8</v>
+      </c>
+    </row>
+    <row r="5759">
+      <c r="A5759" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B5759" t="n">
+        <v>2131.27</v>
+      </c>
+      <c r="C5759" t="n">
+        <v>1981.69</v>
+      </c>
+      <c r="D5759" t="n">
+        <v>60.5</v>
+      </c>
+    </row>
+    <row r="5760">
+      <c r="A5760" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B5760" t="n">
+        <v>2130.07</v>
+      </c>
+      <c r="C5760" t="n">
+        <v>1981.07</v>
+      </c>
+      <c r="D5760" t="n">
+        <v>58.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
@@ -154,7 +154,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-07</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-26</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -266,7 +267,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -423,7 +424,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-07</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-26</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -535,7 +537,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1068,7 +1070,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-Jan-2011 to 07-Oct-2026 (5,759 days). Latest Mazar 2130.07 m (58% of range) on 07-Oct-2026.</t>
+          <t>01-Jan-2011 to 26-Oct-2026 (5,778 days). Latest Mazar 2123.36 m (46% of range) on 26-Oct-2026.</t>
         </is>
       </c>
     </row>
@@ -1396,6 +1398,9 @@
       <c r="F9" t="n">
         <v>2152.44</v>
       </c>
+      <c r="G9" t="n">
+        <v>2128.5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1418,6 +1423,9 @@
       <c r="F10" t="n">
         <v>2152.39</v>
       </c>
+      <c r="G10" t="n">
+        <v>2127.65</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1440,6 +1448,9 @@
       <c r="F11" t="n">
         <v>2152.72</v>
       </c>
+      <c r="G11" t="n">
+        <v>2126.44</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1462,6 +1473,9 @@
       <c r="F12" t="n">
         <v>2153.32</v>
       </c>
+      <c r="G12" t="n">
+        <v>2124.91</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1484,6 +1498,9 @@
       <c r="F13" t="n">
         <v>2153.57</v>
       </c>
+      <c r="G13" t="n">
+        <v>2125.12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1506,6 +1523,9 @@
       <c r="F14" t="n">
         <v>2153.32</v>
       </c>
+      <c r="G14" t="n">
+        <v>2125.45</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1528,6 +1548,9 @@
       <c r="F15" t="n">
         <v>2153.26</v>
       </c>
+      <c r="G15" t="n">
+        <v>2124.46</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1550,6 +1573,9 @@
       <c r="F16" t="n">
         <v>2152.89</v>
       </c>
+      <c r="G16" t="n">
+        <v>2123.53</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1572,6 +1598,9 @@
       <c r="F17" t="n">
         <v>2152.69</v>
       </c>
+      <c r="G17" t="n">
+        <v>2123.52</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1594,6 +1623,9 @@
       <c r="F18" t="n">
         <v>2152.46</v>
       </c>
+      <c r="G18" t="n">
+        <v>2123.17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1616,6 +1648,9 @@
       <c r="F19" t="n">
         <v>2152.31</v>
       </c>
+      <c r="G19" t="n">
+        <v>2122.56</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1638,6 +1673,9 @@
       <c r="F20" t="n">
         <v>2152.55</v>
       </c>
+      <c r="G20" t="n">
+        <v>2121.5</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1660,6 +1698,9 @@
       <c r="F21" t="n">
         <v>2152.45</v>
       </c>
+      <c r="G21" t="n">
+        <v>2120.95</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1682,6 +1723,9 @@
       <c r="F22" t="n">
         <v>2152.38</v>
       </c>
+      <c r="G22" t="n">
+        <v>2121.67</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1704,6 +1748,9 @@
       <c r="F23" t="n">
         <v>2152.32</v>
       </c>
+      <c r="G23" t="n">
+        <v>2122.66</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1726,6 +1773,9 @@
       <c r="F24" t="n">
         <v>2152.12</v>
       </c>
+      <c r="G24" t="n">
+        <v>2123.03</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1748,6 +1798,9 @@
       <c r="F25" t="n">
         <v>2152.04</v>
       </c>
+      <c r="G25" t="n">
+        <v>2123.34</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1770,6 +1823,9 @@
       <c r="F26" t="n">
         <v>2152.13</v>
       </c>
+      <c r="G26" t="n">
+        <v>2123.72</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1791,6 +1847,9 @@
       </c>
       <c r="F27" t="n">
         <v>2152.22</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2123.36</v>
       </c>
     </row>
     <row r="28">
@@ -9573,6 +9632,9 @@
       <c r="F9" t="n">
         <v>1989.72</v>
       </c>
+      <c r="G9" t="n">
+        <v>1980.91</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9595,6 +9657,9 @@
       <c r="F10" t="n">
         <v>1990.34</v>
       </c>
+      <c r="G10" t="n">
+        <v>1979.01</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9617,6 +9682,9 @@
       <c r="F11" t="n">
         <v>1990.21</v>
       </c>
+      <c r="G11" t="n">
+        <v>1978.75</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -9639,6 +9707,9 @@
       <c r="F12" t="n">
         <v>1990.17</v>
       </c>
+      <c r="G12" t="n">
+        <v>1981.26</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -9661,6 +9732,9 @@
       <c r="F13" t="n">
         <v>1990.33</v>
       </c>
+      <c r="G13" t="n">
+        <v>1979.67</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -9683,6 +9757,9 @@
       <c r="F14" t="n">
         <v>1990.6</v>
       </c>
+      <c r="G14" t="n">
+        <v>1971.89</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9705,6 +9782,9 @@
       <c r="F15" t="n">
         <v>1990.25</v>
       </c>
+      <c r="G15" t="n">
+        <v>1972.89</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -9727,6 +9807,9 @@
       <c r="F16" t="n">
         <v>1990.32</v>
       </c>
+      <c r="G16" t="n">
+        <v>1972.83</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -9749,6 +9832,9 @@
       <c r="F17" t="n">
         <v>1989.68</v>
       </c>
+      <c r="G17" t="n">
+        <v>1971.36</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -9771,6 +9857,9 @@
       <c r="F18" t="n">
         <v>1989.45</v>
       </c>
+      <c r="G18" t="n">
+        <v>1971.08</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9793,6 +9882,9 @@
       <c r="F19" t="n">
         <v>1989.27</v>
       </c>
+      <c r="G19" t="n">
+        <v>1970.84</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9815,6 +9907,9 @@
       <c r="F20" t="n">
         <v>1989.16</v>
       </c>
+      <c r="G20" t="n">
+        <v>1972.91</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9837,6 +9932,9 @@
       <c r="F21" t="n">
         <v>1989.35</v>
       </c>
+      <c r="G21" t="n">
+        <v>1972.11</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9859,6 +9957,9 @@
       <c r="F22" t="n">
         <v>1988.78</v>
       </c>
+      <c r="G22" t="n">
+        <v>1974.7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9881,6 +9982,9 @@
       <c r="F23" t="n">
         <v>1988.17</v>
       </c>
+      <c r="G23" t="n">
+        <v>1974.18</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9903,6 +10007,9 @@
       <c r="F24" t="n">
         <v>1988.02</v>
       </c>
+      <c r="G24" t="n">
+        <v>1973.1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9925,6 +10032,9 @@
       <c r="F25" t="n">
         <v>1988.25</v>
       </c>
+      <c r="G25" t="n">
+        <v>1972.65</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9947,6 +10057,9 @@
       <c r="F26" t="n">
         <v>1987.9</v>
       </c>
+      <c r="G26" t="n">
+        <v>1971.64</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9968,6 +10081,9 @@
       </c>
       <c r="F27" t="n">
         <v>1988.01</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1973.35</v>
       </c>
     </row>
     <row r="28">
@@ -17495,7 +17611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5760"/>
+  <dimension ref="A1:D5779"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98144,6 +98260,272 @@
       </c>
       <c r="D5760" t="n">
         <v>58.3</v>
+      </c>
+    </row>
+    <row r="5761">
+      <c r="A5761" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B5761" t="n">
+        <v>2128.5</v>
+      </c>
+      <c r="C5761" t="n">
+        <v>1980.91</v>
+      </c>
+      <c r="D5761" t="n">
+        <v>55.5</v>
+      </c>
+    </row>
+    <row r="5762">
+      <c r="A5762" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B5762" t="n">
+        <v>2127.65</v>
+      </c>
+      <c r="C5762" t="n">
+        <v>1979.01</v>
+      </c>
+      <c r="D5762" t="n">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="5763">
+      <c r="A5763" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B5763" t="n">
+        <v>2126.44</v>
+      </c>
+      <c r="C5763" t="n">
+        <v>1978.75</v>
+      </c>
+      <c r="D5763" t="n">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="5764">
+      <c r="A5764" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B5764" t="n">
+        <v>2124.91</v>
+      </c>
+      <c r="C5764" t="n">
+        <v>1981.26</v>
+      </c>
+      <c r="D5764" t="n">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="5765">
+      <c r="A5765" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B5765" t="n">
+        <v>2125.12</v>
+      </c>
+      <c r="C5765" t="n">
+        <v>1979.67</v>
+      </c>
+      <c r="D5765" t="n">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="5766">
+      <c r="A5766" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B5766" t="n">
+        <v>2125.45</v>
+      </c>
+      <c r="C5766" t="n">
+        <v>1971.89</v>
+      </c>
+      <c r="D5766" t="n">
+        <v>49.9</v>
+      </c>
+    </row>
+    <row r="5767">
+      <c r="A5767" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B5767" t="n">
+        <v>2124.46</v>
+      </c>
+      <c r="C5767" t="n">
+        <v>1972.89</v>
+      </c>
+      <c r="D5767" t="n">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="5768">
+      <c r="A5768" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B5768" t="n">
+        <v>2123.53</v>
+      </c>
+      <c r="C5768" t="n">
+        <v>1972.83</v>
+      </c>
+      <c r="D5768" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="5769">
+      <c r="A5769" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B5769" t="n">
+        <v>2123.52</v>
+      </c>
+      <c r="C5769" t="n">
+        <v>1971.36</v>
+      </c>
+      <c r="D5769" t="n">
+        <v>46.4</v>
+      </c>
+    </row>
+    <row r="5770">
+      <c r="A5770" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B5770" t="n">
+        <v>2123.17</v>
+      </c>
+      <c r="C5770" t="n">
+        <v>1971.08</v>
+      </c>
+      <c r="D5770" t="n">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="5771">
+      <c r="A5771" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B5771" t="n">
+        <v>2122.56</v>
+      </c>
+      <c r="C5771" t="n">
+        <v>1970.84</v>
+      </c>
+      <c r="D5771" t="n">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="5772">
+      <c r="A5772" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B5772" t="n">
+        <v>2121.5</v>
+      </c>
+      <c r="C5772" t="n">
+        <v>1972.91</v>
+      </c>
+      <c r="D5772" t="n">
+        <v>42.7</v>
+      </c>
+    </row>
+    <row r="5773">
+      <c r="A5773" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B5773" t="n">
+        <v>2120.95</v>
+      </c>
+      <c r="C5773" t="n">
+        <v>1972.11</v>
+      </c>
+      <c r="D5773" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="5774">
+      <c r="A5774" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B5774" t="n">
+        <v>2121.67</v>
+      </c>
+      <c r="C5774" t="n">
+        <v>1974.7</v>
+      </c>
+      <c r="D5774" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5775">
+      <c r="A5775" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B5775" t="n">
+        <v>2122.66</v>
+      </c>
+      <c r="C5775" t="n">
+        <v>1974.18</v>
+      </c>
+      <c r="D5775" t="n">
+        <v>44.8</v>
+      </c>
+    </row>
+    <row r="5776">
+      <c r="A5776" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B5776" t="n">
+        <v>2123.03</v>
+      </c>
+      <c r="C5776" t="n">
+        <v>1973.1</v>
+      </c>
+      <c r="D5776" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="5777">
+      <c r="A5777" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B5777" t="n">
+        <v>2123.34</v>
+      </c>
+      <c r="C5777" t="n">
+        <v>1972.65</v>
+      </c>
+      <c r="D5777" t="n">
+        <v>46.1</v>
+      </c>
+    </row>
+    <row r="5778">
+      <c r="A5778" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B5778" t="n">
+        <v>2123.72</v>
+      </c>
+      <c r="C5778" t="n">
+        <v>1971.64</v>
+      </c>
+      <c r="D5778" t="n">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="5779">
+      <c r="A5779" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B5779" t="n">
+        <v>2123.36</v>
+      </c>
+      <c r="C5779" t="n">
+        <v>1973.35</v>
+      </c>
+      <c r="D5779" t="n">
+        <v>46.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
@@ -155,7 +155,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-26</a:t>
+              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -425,7 +425,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-26</a:t>
+              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1070,7 +1070,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-Jan-2011 to 26-Oct-2026 (5,778 days). Latest Mazar 2123.36 m (46% of range) on 26-Oct-2026.</t>
+          <t>01-Jan-2011 to 27-Oct-2026 (5,779 days). Latest Mazar 2122.86 m (45% of range) on 27-Oct-2026.</t>
         </is>
       </c>
     </row>
@@ -1872,6 +1872,9 @@
       </c>
       <c r="F28" t="n">
         <v>2152.62</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2122.86</v>
       </c>
     </row>
     <row r="29">
@@ -10107,6 +10110,9 @@
       <c r="F28" t="n">
         <v>1988.09</v>
       </c>
+      <c r="G28" t="n">
+        <v>1972.01</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17611,7 +17617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5779"/>
+  <dimension ref="A1:D5780"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98526,6 +98532,20 @@
       </c>
       <c r="D5779" t="n">
         <v>46.1</v>
+      </c>
+    </row>
+    <row r="5780">
+      <c r="A5780" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B5780" t="n">
+        <v>2122.86</v>
+      </c>
+      <c r="C5780" t="n">
+        <v>1972.01</v>
+      </c>
+      <c r="D5780" t="n">
+        <v>45.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
@@ -155,7 +155,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -425,7 +425,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1070,7 +1070,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-Jan-2011 to 27-Oct-2026 (5,779 days). Latest Mazar 2122.86 m (45% of range) on 27-Oct-2026.</t>
+          <t>01-Jan-2011 to 28-Oct-2026 (5,780 days). Latest Mazar 2122.56 m (45% of range) on 28-Oct-2026.</t>
         </is>
       </c>
     </row>
@@ -1897,6 +1897,9 @@
       </c>
       <c r="F29" t="n">
         <v>2152.89</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2122.56</v>
       </c>
     </row>
     <row r="30">
@@ -10135,6 +10138,9 @@
       <c r="F29" t="n">
         <v>1989.07</v>
       </c>
+      <c r="G29" t="n">
+        <v>1971.09</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -17617,7 +17623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5780"/>
+  <dimension ref="A1:D5781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98546,6 +98552,20 @@
       </c>
       <c r="D5780" t="n">
         <v>45.2</v>
+      </c>
+    </row>
+    <row r="5781">
+      <c r="A5781" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B5781" t="n">
+        <v>2122.56</v>
+      </c>
+      <c r="C5781" t="n">
+        <v>1971.09</v>
+      </c>
+      <c r="D5781" t="n">
+        <v>44.7</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
@@ -155,7 +155,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -425,7 +425,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1070,7 +1070,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-Jan-2011 to 28-Oct-2026 (5,780 days). Latest Mazar 2122.56 m (45% of range) on 28-Oct-2026.</t>
+          <t>01-Jan-2011 to 29-Oct-2026 (5,781 days). Latest Mazar 2123.03 m (46% of range) on 29-Oct-2026.</t>
         </is>
       </c>
     </row>
@@ -1922,6 +1922,9 @@
       </c>
       <c r="F30" t="n">
         <v>2153.81</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2123.03</v>
       </c>
     </row>
     <row r="31">
@@ -10163,6 +10166,9 @@
       <c r="F30" t="n">
         <v>1989.15</v>
       </c>
+      <c r="G30" t="n">
+        <v>1973.07</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17623,7 +17629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5781"/>
+  <dimension ref="A1:D5782"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98566,6 +98572,20 @@
       </c>
       <c r="D5781" t="n">
         <v>44.7</v>
+      </c>
+    </row>
+    <row r="5782">
+      <c r="A5782" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B5782" t="n">
+        <v>2123.03</v>
+      </c>
+      <c r="C5782" t="n">
+        <v>1973.07</v>
+      </c>
+      <c r="D5782" t="n">
+        <v>45.5</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/ecuador_hydro_reservoirs.xlsx
@@ -155,7 +155,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Ecuador, Mazar reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -425,7 +425,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Ecuador, Amaluza (Paute) reservoir level (CELEC SUR) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1070,7 +1070,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-Jan-2011 to 29-Oct-2026 (5,781 days). Latest Mazar 2123.03 m (46% of range) on 29-Oct-2026.</t>
+          <t>01-Jan-2011 to 30-Oct-2026 (5,782 days). Latest Mazar 2123.59 m (46% of range) on 30-Oct-2026.</t>
         </is>
       </c>
     </row>
@@ -1947,6 +1947,9 @@
       </c>
       <c r="F31" t="n">
         <v>2153.82</v>
+      </c>
+      <c r="G31" t="n">
+        <v>2123.59</v>
       </c>
     </row>
     <row r="32">
@@ -10191,6 +10194,9 @@
       <c r="F31" t="n">
         <v>1989.86</v>
       </c>
+      <c r="G31" t="n">
+        <v>1973.97</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17629,7 +17635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5782"/>
+  <dimension ref="A1:D5783"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98586,6 +98592,20 @@
       </c>
       <c r="D5782" t="n">
         <v>45.5</v>
+      </c>
+    </row>
+    <row r="5783">
+      <c r="A5783" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B5783" t="n">
+        <v>2123.59</v>
+      </c>
+      <c r="C5783" t="n">
+        <v>1973.97</v>
+      </c>
+      <c r="D5783" t="n">
+        <v>46.5</v>
       </c>
     </row>
   </sheetData>
